--- a/ig/DM-37/CodeSystem-TRE-R220-ModeleDocumentCDAStructure.xlsx
+++ b/ig/DM-37/CodeSystem-TRE-R220-ModeleDocumentCDAStructure.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="295" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="304" uniqueCount="212">
   <si>
     <t>Property</t>
   </si>
@@ -64,7 +64,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-03-29T12:00:00+01:00</t>
+    <t>2024-04-26T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -469,9 +469,6 @@
     <t>1.2.250.1.213.1.1.1.51</t>
   </si>
   <si>
-    <t>Synthèse du dossier médical</t>
-  </si>
-  <si>
     <t>1.2.250.1.213.1.1.1.52</t>
   </si>
   <si>
@@ -494,6 +491,21 @@
   </si>
   <si>
     <t>CR d'anatomie et de cytologie pathologiques</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.60</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.61</t>
+  </si>
+  <si>
+    <t>Fiche de transfert vers le service des urgences</t>
+  </si>
+  <si>
+    <t>1.2.250.1.213.1.1.1.62</t>
+  </si>
+  <si>
+    <t>Fiche de retour du service des urgences</t>
   </si>
   <si>
     <t>1.2.250.1.213.1.1.1.8</t>
@@ -1011,7 +1023,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:D80"/>
+  <dimension ref="A1:D83"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <sheetData>
     <row r="1">
@@ -1640,10 +1652,10 @@
         <v>150</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>151</v>
+        <v>63</v>
       </c>
       <c r="D52" t="s" s="2">
-        <v>151</v>
+        <v>63</v>
       </c>
     </row>
     <row r="53">
@@ -1651,13 +1663,13 @@
         <v>49</v>
       </c>
       <c r="B53" t="s" s="2">
+        <v>151</v>
+      </c>
+      <c r="C53" t="s" s="2">
         <v>152</v>
       </c>
-      <c r="C53" t="s" s="2">
-        <v>153</v>
-      </c>
       <c r="D53" t="s" s="2">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="54">
@@ -1665,10 +1677,10 @@
         <v>49</v>
       </c>
       <c r="B54" t="s" s="2">
+        <v>153</v>
+      </c>
+      <c r="C54" t="s" s="2">
         <v>154</v>
-      </c>
-      <c r="C54" t="s" s="2">
-        <v>155</v>
       </c>
       <c r="D54" s="2"/>
     </row>
@@ -1677,10 +1689,10 @@
         <v>49</v>
       </c>
       <c r="B55" t="s" s="2">
+        <v>155</v>
+      </c>
+      <c r="C55" t="s" s="2">
         <v>156</v>
-      </c>
-      <c r="C55" t="s" s="2">
-        <v>157</v>
       </c>
       <c r="D55" s="2"/>
     </row>
@@ -1689,10 +1701,10 @@
         <v>49</v>
       </c>
       <c r="B56" t="s" s="2">
+        <v>157</v>
+      </c>
+      <c r="C56" t="s" s="2">
         <v>158</v>
-      </c>
-      <c r="C56" t="s" s="2">
-        <v>159</v>
       </c>
       <c r="D56" s="2"/>
     </row>
@@ -1701,10 +1713,10 @@
         <v>49</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C57" t="s" s="2">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="D57" s="2"/>
     </row>
@@ -1713,10 +1725,10 @@
         <v>49</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="C58" t="s" s="2">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="D58" s="2"/>
     </row>
@@ -1725,10 +1737,10 @@
         <v>49</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="C59" t="s" s="2">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="D59" s="2"/>
     </row>
@@ -1737,10 +1749,10 @@
         <v>49</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C60" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="D60" s="2"/>
     </row>
@@ -1749,10 +1761,10 @@
         <v>49</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C61" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D61" s="2"/>
     </row>
@@ -1761,10 +1773,10 @@
         <v>49</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C62" t="s" s="2">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="D62" s="2"/>
     </row>
@@ -1773,10 +1785,10 @@
         <v>49</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="C63" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="D63" s="2"/>
     </row>
@@ -1785,10 +1797,10 @@
         <v>49</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C64" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="D64" s="2"/>
     </row>
@@ -1797,10 +1809,10 @@
         <v>49</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="C65" t="s" s="2">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="D65" s="2"/>
     </row>
@@ -1809,10 +1821,10 @@
         <v>49</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C66" t="s" s="2">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D66" s="2"/>
     </row>
@@ -1821,10 +1833,10 @@
         <v>49</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C67" t="s" s="2">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D67" s="2"/>
     </row>
@@ -1833,10 +1845,10 @@
         <v>49</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C68" t="s" s="2">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="D68" s="2"/>
     </row>
@@ -1845,10 +1857,10 @@
         <v>49</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="D69" s="2"/>
     </row>
@@ -1857,10 +1869,10 @@
         <v>49</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="C70" t="s" s="2">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="D70" s="2"/>
     </row>
@@ -1869,10 +1881,10 @@
         <v>49</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="C71" t="s" s="2">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="D71" s="2"/>
     </row>
@@ -1881,10 +1893,10 @@
         <v>49</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D72" s="2"/>
     </row>
@@ -1893,10 +1905,10 @@
         <v>49</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="C73" t="s" s="2">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D73" s="2"/>
     </row>
@@ -1905,10 +1917,10 @@
         <v>49</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="C74" t="s" s="2">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="D74" s="2"/>
     </row>
@@ -1917,10 +1929,10 @@
         <v>49</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="C75" t="s" s="2">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="D75" s="2"/>
     </row>
@@ -1929,10 +1941,10 @@
         <v>49</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="C76" t="s" s="2">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="D76" s="2"/>
     </row>
@@ -1941,10 +1953,10 @@
         <v>49</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="D77" s="2"/>
     </row>
@@ -1953,10 +1965,10 @@
         <v>49</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="C78" t="s" s="2">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="D78" s="2"/>
     </row>
@@ -1965,10 +1977,10 @@
         <v>49</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="C79" t="s" s="2">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D79" s="2"/>
     </row>
@@ -1977,12 +1989,48 @@
         <v>49</v>
       </c>
       <c r="B80" t="s" s="2">
+        <v>204</v>
+      </c>
+      <c r="C80" t="s" s="2">
+        <v>205</v>
+      </c>
+      <c r="D80" s="2"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B81" t="s" s="2">
         <v>206</v>
       </c>
-      <c r="C80" t="s" s="2">
+      <c r="C81" t="s" s="2">
         <v>207</v>
       </c>
-      <c r="D80" s="2"/>
+      <c r="D81" s="2"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B82" t="s" s="2">
+        <v>208</v>
+      </c>
+      <c r="C82" t="s" s="2">
+        <v>209</v>
+      </c>
+      <c r="D82" s="2"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B83" t="s" s="2">
+        <v>210</v>
+      </c>
+      <c r="C83" t="s" s="2">
+        <v>211</v>
+      </c>
+      <c r="D83" s="2"/>
     </row>
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
